--- a/output/pdf_financials_xlsx/DLCG.xlsx
+++ b/output/pdf_financials_xlsx/DLCG.xlsx
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.732</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="35">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.732</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="37">
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.999</v>
+        <v>2.267</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.854</v>
+        <v>2.845</v>
       </c>
     </row>
     <row r="49">
@@ -5893,19 +5893,19 @@
         <v>-21.788</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>-33.307</v>
+        <v>-33.369</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-5.04</v>
+        <v>-5.505</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-20.12</v>
+        <v>-25.639</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>-48.379</v>
+        <v>-48.93</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>-31.425</v>
+        <v>-32.035</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>-5.816</v>
@@ -5932,19 +5932,19 @@
         <v>-21.788</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-33.307</v>
+        <v>-33.369</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-5.04</v>
+        <v>-5.505</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-20.12</v>
+        <v>-25.639</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-48.379</v>
+        <v>-48.93</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-31.425</v>
+        <v>-32.035</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>-5.816</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17248,7 +17248,11 @@
           <t>Lease payments (note 12)</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -18682,7 +18686,11 @@
           <t>Lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -21298,7 +21306,11 @@
           <t>Net lease payments (note 17)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -22944,7 +22956,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -34024,7 +34040,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
